--- a/dataset_t6_grouped/results2/G1/G1_T0374_W0017F0001T0006Z000C1N28_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T0374_W0017F0001T0006Z000C1N28_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>38.09548800485503</v>
+        <v>6.190516800788942</v>
       </c>
       <c r="D2" t="n">
-        <v>32.36826671942074</v>
+        <v>5.25984334190587</v>
       </c>
       <c r="E2" t="n">
-        <v>10.47127547816482</v>
+        <v>1.701582265201783</v>
       </c>
       <c r="F2" t="n">
-        <v>8.072855409138203</v>
+        <v>1.311839003984958</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>24.51862651996708</v>
+        <v>3.98427680949465</v>
       </c>
       <c r="D3" t="n">
-        <v>16.02661694061602</v>
+        <v>2.604325252850103</v>
       </c>
       <c r="E3" t="n">
-        <v>10.47127547816482</v>
+        <v>1.701582265201783</v>
       </c>
       <c r="F3" t="n">
-        <v>8.072855409138203</v>
+        <v>1.311839003984958</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>12.70899483332034</v>
+        <v>2.065211660414556</v>
       </c>
       <c r="D4" t="n">
-        <v>10.91024044748086</v>
+        <v>1.772914072715639</v>
       </c>
       <c r="E4" t="n">
-        <v>10.47127547816482</v>
+        <v>1.701582265201783</v>
       </c>
       <c r="F4" t="n">
-        <v>8.072855409138203</v>
+        <v>1.311839003984958</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>15.60977946680076</v>
+        <v>2.536589163355124</v>
       </c>
       <c r="D5" t="n">
-        <v>11.71537451385998</v>
+        <v>1.903748358502247</v>
       </c>
       <c r="E5" t="n">
-        <v>10.47127547816482</v>
+        <v>1.701582265201783</v>
       </c>
       <c r="F5" t="n">
-        <v>8.072855409138203</v>
+        <v>1.311839003984958</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>22.81283290230166</v>
+        <v>3.707085346624021</v>
       </c>
       <c r="D6" t="n">
-        <v>7.525776265276203</v>
+        <v>1.222938643107383</v>
       </c>
       <c r="E6" t="n">
-        <v>10.47127547816482</v>
+        <v>1.701582265201783</v>
       </c>
       <c r="F6" t="n">
-        <v>8.072855409138203</v>
+        <v>1.311839003984958</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>40.6644497784195</v>
+        <v>6.607973088993168</v>
       </c>
       <c r="D7" t="n">
-        <v>18.69956542089854</v>
+        <v>3.038679380896013</v>
       </c>
       <c r="E7" t="n">
-        <v>10.47127547816482</v>
+        <v>1.701582265201783</v>
       </c>
       <c r="F7" t="n">
-        <v>8.072855409138203</v>
+        <v>1.311839003984958</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
